--- a/AI-inspection/out/AI深度用户占比-软开测试岗(%).xlsx
+++ b/AI-inspection/out/AI深度用户占比-软开测试岗(%).xlsx
@@ -91,7 +91,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.0" customWidth="true"/>
@@ -223,17 +223,17 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>636.0</v>
+        <v>0.0</v>
       </c>
       <c r="K2" t="n">
-        <v>629.0</v>
+        <v>0.0</v>
       </c>
       <c r="L2" t="n">
-        <v>98.9</v>
+        <v>0.0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>127.0</v>
+        <v>0.0</v>
       </c>
       <c r="K7" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" t="n">
-        <v>10.24</v>
+        <v>0.0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -589,17 +589,17 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>134.0</v>
+        <v>4927.0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0</v>
+        <v>4697.0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0</v>
+        <v>95.33</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -894,17 +894,17 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1080.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" t="n">
-        <v>600.0</v>
+        <v>0.0</v>
       </c>
       <c r="L13" t="n">
-        <v>55.56</v>
+        <v>0.0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>101.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" t="n">
         <v>0.0</v>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="K17" t="n">
         <v>0.0</v>
@@ -1199,17 +1199,17 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>322.0</v>
+        <v>0.0</v>
       </c>
       <c r="K18" t="n">
-        <v>281.0</v>
+        <v>0.0</v>
       </c>
       <c r="L18" t="n">
-        <v>87.27</v>
+        <v>0.0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>120.0</v>
+        <v>279.0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>0.0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1443,17 +1443,17 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>311.0</v>
+        <v>0.0</v>
       </c>
       <c r="K22" t="n">
-        <v>246.0</v>
+        <v>0.0</v>
       </c>
       <c r="L22" t="n">
-        <v>79.1</v>
+        <v>0.0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1656.0</v>
+        <v>0.0</v>
       </c>
       <c r="K23" t="n">
-        <v>1601.0</v>
+        <v>0.0</v>
       </c>
       <c r="L23" t="n">
-        <v>96.68</v>
+        <v>0.0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="K25" t="n">
         <v>0.0</v>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3879.0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" t="n">
-        <v>980.0</v>
+        <v>0.0</v>
       </c>
       <c r="L27" t="n">
-        <v>25.26</v>
+        <v>0.0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1870,17 +1870,17 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>54.0</v>
+        <v>0.0</v>
       </c>
       <c r="K29" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="L29" t="n">
-        <v>51.85</v>
+        <v>0.0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="K30" t="n">
         <v>0.0</v>
@@ -2236,17 +2236,17 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>799.0</v>
+        <v>0.0</v>
       </c>
       <c r="K35" t="n">
-        <v>792.0</v>
+        <v>0.0</v>
       </c>
       <c r="L35" t="n">
-        <v>99.12</v>
+        <v>0.0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>344.0</v>
+        <v>0.0</v>
       </c>
       <c r="K36" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
       <c r="L36" t="n">
-        <v>11.05</v>
+        <v>0.0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2480,17 +2480,17 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2501.0</v>
+        <v>4.0</v>
       </c>
       <c r="K39" t="n">
-        <v>2443.0</v>
+        <v>0.0</v>
       </c>
       <c r="L39" t="n">
-        <v>97.68</v>
+        <v>0.0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,17 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>762.0</v>
+        <v>0.0</v>
       </c>
       <c r="K40" t="n">
-        <v>752.0</v>
+        <v>0.0</v>
       </c>
       <c r="L40" t="n">
-        <v>98.69</v>
+        <v>0.0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2602,17 +2602,17 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="K41" t="n">
-        <v>51.0</v>
+        <v>0.0</v>
       </c>
       <c r="L41" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2663,17 +2663,17 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.0</v>
+        <v>172.0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0</v>
+        <v>160.0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0</v>
+        <v>93.02</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>104.0</v>
+        <v>0.0</v>
       </c>
       <c r="K44" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="L44" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>147.0</v>
+        <v>0.0</v>
       </c>
       <c r="K45" t="n">
-        <v>54.0</v>
+        <v>0.0</v>
       </c>
       <c r="L45" t="n">
-        <v>36.73</v>
+        <v>0.0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>32.0</v>
+        <v>12.0</v>
       </c>
       <c r="K46" t="n">
         <v>0.0</v>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>80.0</v>
+        <v>0.0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L48" t="n">
-        <v>1.25</v>
+        <v>0.0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3090,17 +3090,17 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>945.0</v>
+        <v>0.0</v>
       </c>
       <c r="K49" t="n">
-        <v>886.0</v>
+        <v>0.0</v>
       </c>
       <c r="L49" t="n">
-        <v>93.76</v>
+        <v>0.0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3212,13 +3212,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>319.0</v>
+        <v>0.0</v>
       </c>
       <c r="K51" t="n">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
       <c r="L51" t="n">
-        <v>26.96</v>
+        <v>0.0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="K52" t="n">
         <v>0.0</v>
@@ -3517,17 +3517,17 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>54.0</v>
+        <v>0.0</v>
       </c>
       <c r="K56" t="n">
-        <v>42.0</v>
+        <v>0.0</v>
       </c>
       <c r="L56" t="n">
-        <v>77.78</v>
+        <v>0.0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="K59" t="n">
         <v>0.0</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K60" t="n">
         <v>0.0</v>
@@ -3883,17 +3883,17 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>539.0</v>
+        <v>0.0</v>
       </c>
       <c r="K62" t="n">
-        <v>416.0</v>
+        <v>0.0</v>
       </c>
       <c r="L62" t="n">
-        <v>77.18</v>
+        <v>0.0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>46.0</v>
+        <v>0.0</v>
       </c>
       <c r="K63" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L63" t="n">
-        <v>2.17</v>
+        <v>0.0</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="K64" t="n">
         <v>0.0</v>
@@ -4066,17 +4066,17 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="K65" t="n">
-        <v>185.0</v>
+        <v>0.0</v>
       </c>
       <c r="L65" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>276.0</v>
+        <v>0.0</v>
       </c>
       <c r="K66" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="L66" t="n">
-        <v>2.9</v>
+        <v>0.0</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>308.0</v>
+        <v>0.0</v>
       </c>
       <c r="K68" t="n">
         <v>0.0</v>
@@ -4310,17 +4310,17 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>360.0</v>
+        <v>0.0</v>
       </c>
       <c r="K69" t="n">
-        <v>208.0</v>
+        <v>0.0</v>
       </c>
       <c r="L69" t="n">
-        <v>57.78</v>
+        <v>0.0</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4371,17 +4371,17 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>271.0</v>
+        <v>0.0</v>
       </c>
       <c r="K70" t="n">
-        <v>158.0</v>
+        <v>0.0</v>
       </c>
       <c r="L70" t="n">
-        <v>58.3</v>
+        <v>0.0</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4432,17 +4432,17 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>2855.0</v>
+        <v>0.0</v>
       </c>
       <c r="K71" t="n">
-        <v>2809.0</v>
+        <v>0.0</v>
       </c>
       <c r="L71" t="n">
-        <v>98.39</v>
+        <v>0.0</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>163.0</v>
+        <v>0.0</v>
       </c>
       <c r="K73" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L73" t="n">
-        <v>1.23</v>
+        <v>0.0</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4676,17 +4676,17 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>431.0</v>
+        <v>0.0</v>
       </c>
       <c r="K75" t="n">
-        <v>398.0</v>
+        <v>0.0</v>
       </c>
       <c r="L75" t="n">
-        <v>92.34</v>
+        <v>0.0</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4920,17 +4920,17 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>208.0</v>
+        <v>0.0</v>
       </c>
       <c r="K79" t="n">
-        <v>206.0</v>
+        <v>0.0</v>
       </c>
       <c r="L79" t="n">
-        <v>99.04</v>
+        <v>0.0</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4981,17 +4981,17 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>205.0</v>
+        <v>0.0</v>
       </c>
       <c r="K80" t="n">
-        <v>192.0</v>
+        <v>0.0</v>
       </c>
       <c r="L80" t="n">
-        <v>93.66</v>
+        <v>0.0</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5103,13 +5103,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>277.0</v>
+        <v>0.0</v>
       </c>
       <c r="K82" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="L82" t="n">
-        <v>5.42</v>
+        <v>0.0</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5181,12 +5181,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>zhengyehui.1</t>
+          <t>zhouzhenjiang3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>郑业辉</t>
+          <t>周振江</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="K84" t="n">
         <v>0.0</v>
@@ -5242,12 +5242,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>zhouzhenjiang3</t>
+          <t>zhutao36</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>周振江</t>
+          <t>朱涛</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="K85" t="n">
         <v>0.0</v>
@@ -5295,67 +5295,6 @@
         <v>0.0</v>
       </c>
       <c r="M85" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>zhutao36</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>朱涛</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>软件开发岗</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>京东集团-京东科技-金融科技事业群-金融科技研发部-支付方案研发部</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>京东科技</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>金融科技事业群</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>金融科技研发部</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>支付方案研发部</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M86" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -5419,7 +5358,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5370,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
